--- a/M241_M245_Ideenformularvorlage_IMS.xlsx
+++ b/M241_M245_Ideenformularvorlage_IMS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\poles\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\poles\Desktop\M241\M241-JourneyMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02000277-6C4F-4241-B82A-6BDB3A674219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE0F30D-A7DB-4C19-849F-D7D521E8D51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="96">
   <si>
     <t>Ideenformular (1 Idee pro Register) · Modul 241/245</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>Eine Umfrage mit potenziellen Nutzern durchgeführen</t>
+  </si>
+  <si>
+    <t>e</t>
   </si>
 </sst>
 </file>
@@ -488,46 +491,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -550,10 +553,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -772,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I102"/>
+  <dimension ref="B2:BG102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -781,423 +780,434 @@
     <col min="4" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+    <row r="2" spans="2:59" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="26" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="2:59" x14ac:dyDescent="0.3">
+      <c r="B3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-    </row>
-    <row r="4" spans="2:9" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-    </row>
-    <row r="6" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="19" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="2:59" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="BF4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="2:59" x14ac:dyDescent="0.3">
+      <c r="BF5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="2:59" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="21" t="s">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-    </row>
-    <row r="8" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="13"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="2:59" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="21" t="s">
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="2:9" ht="112.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="13"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="2:59" ht="112.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-    </row>
-    <row r="11" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21" t="s">
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-    </row>
-    <row r="12" spans="2:9" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="13"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" spans="2:59" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-    </row>
-    <row r="13" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21" t="s">
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-    </row>
-    <row r="14" spans="2:9" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="13"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="2:59" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="10" t="s">
         <v>86</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-    </row>
-    <row r="15" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21" t="s">
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-    </row>
-    <row r="16" spans="2:9" ht="114" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="13"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="2:59" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C16" s="11"/>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
     </row>
     <row r="21" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
     </row>
     <row r="23" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
     </row>
     <row r="27" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
     </row>
     <row r="29" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
     </row>
     <row r="33" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
     </row>
     <row r="37" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8" t="s">
@@ -1209,13 +1219,13 @@
       <c r="D37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
     </row>
     <row r="38" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
@@ -1225,11 +1235,11 @@
         <v>38</v>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
     </row>
     <row r="39" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
@@ -1239,11 +1249,11 @@
         <v>39</v>
       </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
     </row>
     <row r="40" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
@@ -1253,11 +1263,11 @@
         <v>40</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
     </row>
     <row r="41" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
@@ -1267,11 +1277,11 @@
         <v>41</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
     </row>
     <row r="42" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
@@ -1281,11 +1291,11 @@
         <v>43</v>
       </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
     </row>
     <row r="43" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
@@ -1295,11 +1305,11 @@
         <v>44</v>
       </c>
       <c r="D43" s="4"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
     </row>
     <row r="44" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
@@ -1309,11 +1319,11 @@
         <v>46</v>
       </c>
       <c r="D44" s="4"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
     </row>
     <row r="45" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
@@ -1323,11 +1333,11 @@
         <v>47</v>
       </c>
       <c r="D45" s="4"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
     </row>
     <row r="46" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
@@ -1337,11 +1347,11 @@
         <v>49</v>
       </c>
       <c r="D46" s="4"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
     </row>
     <row r="47" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
@@ -1351,35 +1361,35 @@
         <v>50</v>
       </c>
       <c r="D47" s="4"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
     </row>
     <row r="48" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
     </row>
     <row r="50" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
     </row>
     <row r="51" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="s">
@@ -1466,14 +1476,14 @@
     </row>
     <row r="64" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
       <c r="H65" s="6">
         <f>SUM(H52:H63)</f>
         <v>0</v>
@@ -1482,265 +1492,265 @@
     <row r="66" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
     </row>
     <row r="69" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16" t="s">
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
     </row>
     <row r="70" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="7">
         <v>1</v>
       </c>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="23"/>
+      <c r="H70" s="23"/>
+      <c r="I70" s="23"/>
     </row>
     <row r="71" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="7">
         <v>2</v>
       </c>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="23"/>
+      <c r="I71" s="23"/>
     </row>
     <row r="72" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="7">
         <v>3</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
+      <c r="C72" s="23"/>
+      <c r="D72" s="23"/>
+      <c r="E72" s="23"/>
+      <c r="F72" s="23"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="23"/>
+      <c r="I72" s="23"/>
     </row>
     <row r="73" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="7">
         <v>4</v>
       </c>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="23"/>
+      <c r="I73" s="23"/>
     </row>
     <row r="74" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="7">
         <v>5</v>
       </c>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
     </row>
     <row r="75" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="7">
         <v>6</v>
       </c>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="23"/>
+      <c r="I75" s="23"/>
     </row>
     <row r="76" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="7">
         <v>7</v>
       </c>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="23"/>
     </row>
     <row r="77" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="7">
         <v>8</v>
       </c>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
+      <c r="I77" s="23"/>
     </row>
     <row r="78" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="7">
         <v>9</v>
       </c>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
+      <c r="C78" s="23"/>
+      <c r="D78" s="23"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
     </row>
     <row r="79" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="7">
         <v>10</v>
       </c>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
+      <c r="C79" s="23"/>
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
     </row>
     <row r="80" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
+      <c r="C80" s="23"/>
+      <c r="D80" s="23"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="23"/>
+      <c r="G80" s="23"/>
+      <c r="H80" s="23"/>
+      <c r="I80" s="23"/>
     </row>
     <row r="81" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="82" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
     </row>
     <row r="83" spans="2:9" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
     </row>
     <row r="84" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16" t="s">
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="H84" s="16"/>
-      <c r="I84" s="16"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="22"/>
     </row>
     <row r="85" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="7"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="23"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="23"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="23"/>
+      <c r="I85" s="23"/>
     </row>
     <row r="86" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="7"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="23"/>
+      <c r="I86" s="23"/>
     </row>
     <row r="87" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="7"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
+      <c r="C87" s="23"/>
+      <c r="D87" s="23"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="23"/>
+      <c r="G87" s="23"/>
+      <c r="H87" s="23"/>
+      <c r="I87" s="23"/>
     </row>
     <row r="88" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="7"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
+      <c r="I88" s="23"/>
     </row>
     <row r="89" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="23"/>
+      <c r="I89" s="23"/>
     </row>
     <row r="90" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="7"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="23"/>
+      <c r="I90" s="23"/>
     </row>
     <row r="91" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="2:9" ht="20.85" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1755,47 +1765,42 @@
     <row r="102" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="B3:I4"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="C88:F88"/>
+    <mergeCell ref="G88:I88"/>
+    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="G90:I90"/>
+    <mergeCell ref="C85:F85"/>
+    <mergeCell ref="G85:I85"/>
+    <mergeCell ref="C86:F86"/>
+    <mergeCell ref="G86:I86"/>
+    <mergeCell ref="C87:F87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="B83:I83"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="G79:I79"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="G74:I74"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="G73:I73"/>
     <mergeCell ref="B68:I68"/>
     <mergeCell ref="C69:F69"/>
     <mergeCell ref="G69:I69"/>
@@ -1820,42 +1825,47 @@
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="G74:I74"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="G72:I72"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="G73:I73"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="C88:F88"/>
-    <mergeCell ref="G88:I88"/>
-    <mergeCell ref="C89:F89"/>
-    <mergeCell ref="G89:I89"/>
-    <mergeCell ref="C90:F90"/>
-    <mergeCell ref="G90:I90"/>
-    <mergeCell ref="C85:F85"/>
-    <mergeCell ref="G85:I85"/>
-    <mergeCell ref="C86:F86"/>
-    <mergeCell ref="G86:I86"/>
-    <mergeCell ref="C87:F87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="B80:I80"/>
-    <mergeCell ref="B82:I82"/>
-    <mergeCell ref="B83:I83"/>
-    <mergeCell ref="C84:F84"/>
-    <mergeCell ref="G84:I84"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="G77:I77"/>
-    <mergeCell ref="C78:F78"/>
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="C79:F79"/>
-    <mergeCell ref="G79:I79"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D10:I10"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="D38 D39 D40 D41 D42 D43 D44 D45 D46 D47" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1887,422 +1897,422 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
     </row>
     <row r="4" spans="2:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="6" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
     </row>
     <row r="7" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
     </row>
     <row r="9" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="2:9" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
         <v>90</v>
       </c>
       <c r="C10" s="28"/>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
     </row>
     <row r="12" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="27" t="s">
         <v>91</v>
       </c>
       <c r="C12" s="28"/>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
     </row>
     <row r="13" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" spans="2:9" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C14" s="28"/>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
     </row>
     <row r="16" spans="2:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
         <v>93</v>
       </c>
       <c r="C16" s="28"/>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="2:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
         <v>94</v>
       </c>
       <c r="C18" s="28"/>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
     </row>
     <row r="21" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
     </row>
     <row r="23" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
     </row>
     <row r="27" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
     </row>
     <row r="29" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
     </row>
     <row r="33" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
     </row>
     <row r="37" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8" t="s">
@@ -2314,13 +2324,13 @@
       <c r="D37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
     </row>
     <row r="38" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
@@ -2330,11 +2340,11 @@
         <v>38</v>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
     </row>
     <row r="39" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
@@ -2344,11 +2354,11 @@
         <v>39</v>
       </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
     </row>
     <row r="40" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
@@ -2358,11 +2368,11 @@
         <v>40</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
     </row>
     <row r="41" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
@@ -2372,11 +2382,11 @@
         <v>41</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
     </row>
     <row r="42" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
@@ -2386,11 +2396,11 @@
         <v>43</v>
       </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
     </row>
     <row r="43" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
@@ -2400,11 +2410,11 @@
         <v>44</v>
       </c>
       <c r="D43" s="4"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
     </row>
     <row r="44" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
@@ -2414,11 +2424,11 @@
         <v>46</v>
       </c>
       <c r="D44" s="4"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
     </row>
     <row r="45" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
@@ -2428,11 +2438,11 @@
         <v>47</v>
       </c>
       <c r="D45" s="4"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
     </row>
     <row r="46" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
@@ -2442,11 +2452,11 @@
         <v>49</v>
       </c>
       <c r="D46" s="4"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
     </row>
     <row r="47" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
@@ -2456,35 +2466,35 @@
         <v>50</v>
       </c>
       <c r="D47" s="4"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
     </row>
     <row r="48" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
     </row>
     <row r="50" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
     </row>
     <row r="51" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="s">
@@ -2571,14 +2581,14 @@
     </row>
     <row r="64" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
       <c r="H65" s="6">
         <f>SUM(H52:H63)</f>
         <v>0</v>
@@ -2587,265 +2597,265 @@
     <row r="66" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
     </row>
     <row r="69" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16" t="s">
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
     </row>
     <row r="70" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="7">
         <v>1</v>
       </c>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="23"/>
+      <c r="H70" s="23"/>
+      <c r="I70" s="23"/>
     </row>
     <row r="71" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="7">
         <v>2</v>
       </c>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="23"/>
+      <c r="I71" s="23"/>
     </row>
     <row r="72" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="7">
         <v>3</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
+      <c r="C72" s="23"/>
+      <c r="D72" s="23"/>
+      <c r="E72" s="23"/>
+      <c r="F72" s="23"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="23"/>
+      <c r="I72" s="23"/>
     </row>
     <row r="73" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="7">
         <v>4</v>
       </c>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="23"/>
+      <c r="I73" s="23"/>
     </row>
     <row r="74" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="7">
         <v>5</v>
       </c>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
     </row>
     <row r="75" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="7">
         <v>6</v>
       </c>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="23"/>
+      <c r="I75" s="23"/>
     </row>
     <row r="76" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="7">
         <v>7</v>
       </c>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="23"/>
     </row>
     <row r="77" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="7">
         <v>8</v>
       </c>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
+      <c r="I77" s="23"/>
     </row>
     <row r="78" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="7">
         <v>9</v>
       </c>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
+      <c r="C78" s="23"/>
+      <c r="D78" s="23"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
     </row>
     <row r="79" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="7">
         <v>10</v>
       </c>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
+      <c r="C79" s="23"/>
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
     </row>
     <row r="80" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
+      <c r="C80" s="23"/>
+      <c r="D80" s="23"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="23"/>
+      <c r="G80" s="23"/>
+      <c r="H80" s="23"/>
+      <c r="I80" s="23"/>
     </row>
     <row r="81" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="82" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
     </row>
     <row r="83" spans="2:9" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C83" s="15"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
     </row>
     <row r="84" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16" t="s">
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="H84" s="16"/>
-      <c r="I84" s="16"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="22"/>
     </row>
     <row r="85" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="7"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="23"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="23"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="23"/>
+      <c r="I85" s="23"/>
     </row>
     <row r="86" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="7"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="23"/>
+      <c r="I86" s="23"/>
     </row>
     <row r="87" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="7"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
+      <c r="C87" s="23"/>
+      <c r="D87" s="23"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="23"/>
+      <c r="G87" s="23"/>
+      <c r="H87" s="23"/>
+      <c r="I87" s="23"/>
     </row>
     <row r="88" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="7"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
+      <c r="I88" s="23"/>
     </row>
     <row r="89" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="23"/>
+      <c r="I89" s="23"/>
     </row>
     <row r="90" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="7"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="23"/>
+      <c r="I90" s="23"/>
     </row>
     <row r="91" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="2:9" ht="20.85" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2860,28 +2870,77 @@
     <row r="102" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="106">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I4"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="G90:I90"/>
+    <mergeCell ref="C86:F86"/>
+    <mergeCell ref="G86:I86"/>
+    <mergeCell ref="C87:F87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="C88:F88"/>
+    <mergeCell ref="G88:I88"/>
+    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="B83:I83"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="C85:F85"/>
+    <mergeCell ref="G85:I85"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="G79:I79"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="G74:I74"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="G73:I73"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="E39:I39"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:I28"/>
     <mergeCell ref="D21:I21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:I22"/>
@@ -2895,77 +2954,28 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="G70:I70"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="E47:I47"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="G74:I74"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="G72:I72"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="G73:I73"/>
-    <mergeCell ref="B80:I80"/>
-    <mergeCell ref="B82:I82"/>
-    <mergeCell ref="B83:I83"/>
-    <mergeCell ref="C84:F84"/>
-    <mergeCell ref="G84:I84"/>
-    <mergeCell ref="C85:F85"/>
-    <mergeCell ref="G85:I85"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="G77:I77"/>
-    <mergeCell ref="C78:F78"/>
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="C79:F79"/>
-    <mergeCell ref="G79:I79"/>
-    <mergeCell ref="C89:F89"/>
-    <mergeCell ref="G89:I89"/>
-    <mergeCell ref="C90:F90"/>
-    <mergeCell ref="G90:I90"/>
-    <mergeCell ref="C86:F86"/>
-    <mergeCell ref="G86:I86"/>
-    <mergeCell ref="C87:F87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="C88:F88"/>
-    <mergeCell ref="G88:I88"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D14:I14"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="B97:B102" xr:uid="{7EDD4AA0-6882-4598-BDB5-AA1AA54156E4}">
@@ -2986,6 +2996,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7428d6b1-3919-45ca-a810-a9f24c98c389" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100474F511FE9344346B3B565D439640D46" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="21da785c10f7c5f43f37cca8904c7fb7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7428d6b1-3919-45ca-a810-a9f24c98c389" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="602e5a62d6284efa4700467c044525af" ns3:_="">
     <xsd:import namespace="7428d6b1-3919-45ca-a810-a9f24c98c389"/>
@@ -3179,37 +3206,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7428d6b1-3919-45ca-a810-a9f24c98c389" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FADA5DF-D87A-40F2-8D79-31DE0B4C9DB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52DFF2B8-7373-4220-859A-6E9CD68C3781}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7428d6b1-3919-45ca-a810-a9f24c98c389"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3231,9 +3231,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52DFF2B8-7373-4220-859A-6E9CD68C3781}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FADA5DF-D87A-40F2-8D79-31DE0B4C9DB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7428d6b1-3919-45ca-a810-a9f24c98c389"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/M241_M245_Ideenformularvorlage_IMS.xlsx
+++ b/M241_M245_Ideenformularvorlage_IMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\poles\Desktop\M241\M241-JourneyMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE0F30D-A7DB-4C19-849F-D7D521E8D51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC5F960-DB7C-4528-98A4-499081DA32E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ideenformular #1" sheetId="1" r:id="rId1"/>
@@ -320,9 +320,6 @@
     <t>In Städten und dicht besiedelten Gebieten gibt es oft wenige Parkplätze gleichzeitig werden viele nicht genutzt wegen der Arbeit oder dem Urlaub. Es fehlt eine Möglichkeit, diese freien Parkfächem kutzfristig anderen zur Verfügung zu stellen.</t>
   </si>
   <si>
-    <t>Personen mit einem privaten Parkplatz, der zeitweise nicht genutzt wird, Autofahrer, die kurzfristig einen Parkplatz suchen</t>
-  </si>
-  <si>
     <t>Statt neue Parkplätze zu bauen, werden bereits vorhandene, aber ungenutzte Flächen effizienter verwendet. Besonders interessant ist die flexible Vermietung nach Zeitfenstern, beispielsweise nur während der Arbeitszeit oder während Ferien.</t>
   </si>
   <si>
@@ -330,6 +327,9 @@
   </si>
   <si>
     <t>e</t>
+  </si>
+  <si>
+    <t>Personen mit einem privaten Parkplatz, der zeitweise nicht genutzt wird, Autofahrer, die kurzfristig einen Parkplatz suchen.</t>
   </si>
 </sst>
 </file>
@@ -491,46 +491,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -781,433 +781,433 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:59" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
     </row>
     <row r="3" spans="2:59" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
     </row>
     <row r="4" spans="2:59" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
       <c r="BF4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="BG4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="2:59" x14ac:dyDescent="0.3">
       <c r="BF5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="2:59" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
     </row>
     <row r="7" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" spans="2:59" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
     </row>
     <row r="9" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="2:59" ht="112.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C10" s="11"/>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" spans="2:59" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
     </row>
     <row r="13" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
     </row>
     <row r="14" spans="2:59" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="10" t="s">
         <v>86</v>
       </c>
       <c r="C14" s="11"/>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
     </row>
     <row r="15" spans="2:59" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
     </row>
     <row r="16" spans="2:59" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C16" s="11"/>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="17" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
     </row>
     <row r="18" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
     </row>
     <row r="19" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
     </row>
     <row r="20" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
     </row>
     <row r="21" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
     </row>
     <row r="22" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
     </row>
     <row r="24" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
     </row>
     <row r="25" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
     </row>
     <row r="26" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
     </row>
     <row r="27" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
     </row>
     <row r="28" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
     </row>
     <row r="30" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
     </row>
     <row r="31" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
     </row>
     <row r="32" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
     </row>
     <row r="33" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
     </row>
     <row r="34" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
     </row>
     <row r="35" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
     </row>
     <row r="36" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
     </row>
     <row r="37" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8" t="s">
@@ -1219,13 +1219,13 @@
       <c r="D37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
     </row>
     <row r="38" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
@@ -1235,11 +1235,11 @@
         <v>38</v>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
     </row>
     <row r="39" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
@@ -1249,11 +1249,11 @@
         <v>39</v>
       </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
     </row>
     <row r="40" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
@@ -1263,11 +1263,11 @@
         <v>40</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
     </row>
     <row r="41" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
@@ -1277,11 +1277,11 @@
         <v>41</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
     </row>
     <row r="42" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
@@ -1291,11 +1291,11 @@
         <v>43</v>
       </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
     </row>
     <row r="43" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
@@ -1305,11 +1305,11 @@
         <v>44</v>
       </c>
       <c r="D43" s="4"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
     </row>
     <row r="44" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
@@ -1319,11 +1319,11 @@
         <v>46</v>
       </c>
       <c r="D44" s="4"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
     </row>
     <row r="45" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
@@ -1333,11 +1333,11 @@
         <v>47</v>
       </c>
       <c r="D45" s="4"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
     </row>
     <row r="46" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
@@ -1347,11 +1347,11 @@
         <v>49</v>
       </c>
       <c r="D46" s="4"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
     </row>
     <row r="47" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
@@ -1361,35 +1361,35 @@
         <v>50</v>
       </c>
       <c r="D47" s="4"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
     </row>
     <row r="48" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
     </row>
     <row r="50" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
     </row>
     <row r="51" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="s">
@@ -1476,14 +1476,14 @@
     </row>
     <row r="64" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
       <c r="H65" s="6">
         <f>SUM(H52:H63)</f>
         <v>0</v>
@@ -1492,265 +1492,265 @@
     <row r="66" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="21" t="s">
+      <c r="B68" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
     </row>
     <row r="69" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22" t="s">
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
     </row>
     <row r="70" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="7">
         <v>1</v>
       </c>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
     </row>
     <row r="71" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="7">
         <v>2</v>
       </c>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
     </row>
     <row r="72" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="7">
         <v>3</v>
       </c>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
     </row>
     <row r="73" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="7">
         <v>4</v>
       </c>
-      <c r="C73" s="23"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
     </row>
     <row r="74" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="7">
         <v>5</v>
       </c>
-      <c r="C74" s="23"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="23"/>
-      <c r="I74" s="23"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
     </row>
     <row r="75" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="7">
         <v>6</v>
       </c>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
     </row>
     <row r="76" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="7">
         <v>7</v>
       </c>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
     </row>
     <row r="77" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="7">
         <v>8</v>
       </c>
-      <c r="C77" s="23"/>
-      <c r="D77" s="23"/>
-      <c r="E77" s="23"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
     </row>
     <row r="78" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="7">
         <v>9</v>
       </c>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
     </row>
     <row r="79" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="7">
         <v>10</v>
       </c>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
     </row>
     <row r="80" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="23" t="s">
+      <c r="B80" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
     </row>
     <row r="81" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="82" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="21" t="s">
+      <c r="B82" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C82" s="21"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
-      <c r="I82" s="21"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
     </row>
     <row r="83" spans="2:9" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="26" t="s">
+      <c r="B83" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C83" s="26"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26"/>
-      <c r="G83" s="26"/>
-      <c r="H83" s="26"/>
-      <c r="I83" s="26"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
     </row>
     <row r="84" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C84" s="22" t="s">
+      <c r="C84" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D84" s="22"/>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
-      <c r="G84" s="22" t="s">
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="H84" s="22"/>
-      <c r="I84" s="22"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
     </row>
     <row r="85" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="7"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="23"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="23"/>
-      <c r="H85" s="23"/>
-      <c r="I85" s="23"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
     </row>
     <row r="86" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="7"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="23"/>
-      <c r="G86" s="23"/>
-      <c r="H86" s="23"/>
-      <c r="I86" s="23"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
     </row>
     <row r="87" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="7"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="23"/>
-      <c r="H87" s="23"/>
-      <c r="I87" s="23"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
     </row>
     <row r="88" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="7"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="23"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
     </row>
     <row r="89" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="23"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
     </row>
     <row r="90" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="7"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="23"/>
-      <c r="I90" s="23"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
     </row>
     <row r="91" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="2:9" ht="20.85" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1765,6 +1765,83 @@
     <row r="102" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E39:I39"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="G74:I74"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="G73:I73"/>
     <mergeCell ref="B65:G65"/>
     <mergeCell ref="C88:F88"/>
     <mergeCell ref="G88:I88"/>
@@ -1789,83 +1866,6 @@
     <mergeCell ref="G78:I78"/>
     <mergeCell ref="C79:F79"/>
     <mergeCell ref="G79:I79"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="G74:I74"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="G72:I72"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="G73:I73"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="G70:I70"/>
-    <mergeCell ref="E47:I47"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="B3:I4"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D10:I10"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="D38 D39 D40 D41 D42 D43 D44 D45 D46 D47" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1897,422 +1897,422 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="20.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
     </row>
     <row r="4" spans="2:9" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
     </row>
     <row r="6" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
     </row>
     <row r="7" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
     </row>
     <row r="9" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="2:9" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
         <v>90</v>
       </c>
       <c r="C10" s="28"/>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" spans="2:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="27" t="s">
         <v>91</v>
       </c>
       <c r="C12" s="28"/>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
     </row>
     <row r="13" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
     </row>
     <row r="14" spans="2:9" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" s="28"/>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
     </row>
     <row r="15" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
     </row>
     <row r="16" spans="2:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="28"/>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="17" spans="2:9" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
     </row>
     <row r="18" spans="2:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="28"/>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
     </row>
     <row r="19" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
     </row>
     <row r="20" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
     </row>
     <row r="21" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
     </row>
     <row r="22" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
     </row>
     <row r="24" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
     </row>
     <row r="25" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
     </row>
     <row r="26" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
     </row>
     <row r="27" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
     </row>
     <row r="28" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
     </row>
     <row r="30" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
     </row>
     <row r="31" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
     </row>
     <row r="32" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
     </row>
     <row r="33" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
     </row>
     <row r="34" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
     </row>
     <row r="35" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
     </row>
     <row r="36" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
     </row>
     <row r="37" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8" t="s">
@@ -2324,13 +2324,13 @@
       <c r="D37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
     </row>
     <row r="38" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
@@ -2340,11 +2340,11 @@
         <v>38</v>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
     </row>
     <row r="39" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
@@ -2354,11 +2354,11 @@
         <v>39</v>
       </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
     </row>
     <row r="40" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
@@ -2368,11 +2368,11 @@
         <v>40</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
     </row>
     <row r="41" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
@@ -2382,11 +2382,11 @@
         <v>41</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
     </row>
     <row r="42" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
@@ -2396,11 +2396,11 @@
         <v>43</v>
       </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
     </row>
     <row r="43" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
@@ -2410,11 +2410,11 @@
         <v>44</v>
       </c>
       <c r="D43" s="4"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
     </row>
     <row r="44" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
@@ -2424,11 +2424,11 @@
         <v>46</v>
       </c>
       <c r="D44" s="4"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
     </row>
     <row r="45" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
@@ -2438,11 +2438,11 @@
         <v>47</v>
       </c>
       <c r="D45" s="4"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
     </row>
     <row r="46" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
@@ -2452,11 +2452,11 @@
         <v>49</v>
       </c>
       <c r="D46" s="4"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
     </row>
     <row r="47" spans="2:9" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
@@ -2466,35 +2466,35 @@
         <v>50</v>
       </c>
       <c r="D47" s="4"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
     </row>
     <row r="48" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
     </row>
     <row r="50" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
     </row>
     <row r="51" spans="2:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8" t="s">
@@ -2581,14 +2581,14 @@
     </row>
     <row r="64" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
       <c r="H65" s="6">
         <f>SUM(H52:H63)</f>
         <v>0</v>
@@ -2597,265 +2597,265 @@
     <row r="66" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="21" t="s">
+      <c r="B68" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
     </row>
     <row r="69" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22" t="s">
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
     </row>
     <row r="70" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="7">
         <v>1</v>
       </c>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
     </row>
     <row r="71" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="7">
         <v>2</v>
       </c>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
     </row>
     <row r="72" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="7">
         <v>3</v>
       </c>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
     </row>
     <row r="73" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="7">
         <v>4</v>
       </c>
-      <c r="C73" s="23"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
     </row>
     <row r="74" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="7">
         <v>5</v>
       </c>
-      <c r="C74" s="23"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="23"/>
-      <c r="I74" s="23"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
     </row>
     <row r="75" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="7">
         <v>6</v>
       </c>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
     </row>
     <row r="76" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="7">
         <v>7</v>
       </c>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
     </row>
     <row r="77" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="7">
         <v>8</v>
       </c>
-      <c r="C77" s="23"/>
-      <c r="D77" s="23"/>
-      <c r="E77" s="23"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
     </row>
     <row r="78" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="7">
         <v>9</v>
       </c>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
     </row>
     <row r="79" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="7">
         <v>10</v>
       </c>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
     </row>
     <row r="80" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="23" t="s">
+      <c r="B80" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
     </row>
     <row r="81" spans="2:9" ht="6.45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="82" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="21" t="s">
+      <c r="B82" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C82" s="21"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
-      <c r="I82" s="21"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
     </row>
     <row r="83" spans="2:9" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="26" t="s">
+      <c r="B83" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C83" s="26"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26"/>
-      <c r="G83" s="26"/>
-      <c r="H83" s="26"/>
-      <c r="I83" s="26"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
     </row>
     <row r="84" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C84" s="22" t="s">
+      <c r="C84" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D84" s="22"/>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
-      <c r="G84" s="22" t="s">
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="H84" s="22"/>
-      <c r="I84" s="22"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
     </row>
     <row r="85" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="7"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="23"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="23"/>
-      <c r="H85" s="23"/>
-      <c r="I85" s="23"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
     </row>
     <row r="86" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="7"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="23"/>
-      <c r="G86" s="23"/>
-      <c r="H86" s="23"/>
-      <c r="I86" s="23"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
     </row>
     <row r="87" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="7"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="23"/>
-      <c r="H87" s="23"/>
-      <c r="I87" s="23"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
     </row>
     <row r="88" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="7"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="23"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
     </row>
     <row r="89" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="23"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
     </row>
     <row r="90" spans="2:9" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="7"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="23"/>
-      <c r="I90" s="23"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
     </row>
     <row r="91" spans="2:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="2:9" ht="20.85" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2870,16 +2870,89 @@
     <row r="102" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="106">
-    <mergeCell ref="C89:F89"/>
-    <mergeCell ref="G89:I89"/>
-    <mergeCell ref="C90:F90"/>
-    <mergeCell ref="G90:I90"/>
-    <mergeCell ref="C86:F86"/>
-    <mergeCell ref="G86:I86"/>
-    <mergeCell ref="C87:F87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="C88:F88"/>
-    <mergeCell ref="G88:I88"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="E39:I39"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="E45:I45"/>
+    <mergeCell ref="E46:I46"/>
+    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="G74:I74"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="G73:I73"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="B82:I82"/>
     <mergeCell ref="B83:I83"/>
@@ -2893,89 +2966,16 @@
     <mergeCell ref="G78:I78"/>
     <mergeCell ref="C79:F79"/>
     <mergeCell ref="G79:I79"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="G74:I74"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="G72:I72"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="G73:I73"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="G70:I70"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="E46:I46"/>
-    <mergeCell ref="E47:I47"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:I24"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I4"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="G90:I90"/>
+    <mergeCell ref="C86:F86"/>
+    <mergeCell ref="G86:I86"/>
+    <mergeCell ref="C87:F87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="C88:F88"/>
+    <mergeCell ref="G88:I88"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="B97:B102" xr:uid="{7EDD4AA0-6882-4598-BDB5-AA1AA54156E4}">
@@ -2996,23 +2996,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7428d6b1-3919-45ca-a810-a9f24c98c389" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100474F511FE9344346B3B565D439640D46" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="21da785c10f7c5f43f37cca8904c7fb7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7428d6b1-3919-45ca-a810-a9f24c98c389" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="602e5a62d6284efa4700467c044525af" ns3:_="">
     <xsd:import namespace="7428d6b1-3919-45ca-a810-a9f24c98c389"/>
@@ -3206,10 +3189,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7428d6b1-3919-45ca-a810-a9f24c98c389" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52DFF2B8-7373-4220-859A-6E9CD68C3781}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FADA5DF-D87A-40F2-8D79-31DE0B4C9DB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7428d6b1-3919-45ca-a810-a9f24c98c389"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3231,19 +3241,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FADA5DF-D87A-40F2-8D79-31DE0B4C9DB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52DFF2B8-7373-4220-859A-6E9CD68C3781}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7428d6b1-3919-45ca-a810-a9f24c98c389"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/M241_M245_Ideenformularvorlage_IMS.xlsx
+++ b/M241_M245_Ideenformularvorlage_IMS.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC5F960-DB7C-4528-98A4-499081DA32E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ideenformular #1" sheetId="1" r:id="rId1"/>
